--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N88_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N88_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>86.44542817529658</v>
+        <v>14.0473820784857</v>
       </c>
       <c r="D2" t="n">
-        <v>86.31600892192388</v>
+        <v>14.02635144981263</v>
       </c>
       <c r="E2" t="n">
-        <v>12.39015753321636</v>
+        <v>2.013400599147659</v>
       </c>
       <c r="F2" t="n">
-        <v>11.95764903136709</v>
+        <v>1.943117967597153</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>60.03813239606107</v>
+        <v>9.756196514359923</v>
       </c>
       <c r="D3" t="n">
-        <v>60.94571538614502</v>
+        <v>9.903678750248567</v>
       </c>
       <c r="E3" t="n">
-        <v>12.39015753321636</v>
+        <v>2.013400599147659</v>
       </c>
       <c r="F3" t="n">
-        <v>11.95764903136709</v>
+        <v>1.943117967597153</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.49963831840006</v>
+        <v>8.53119122674001</v>
       </c>
       <c r="D4" t="n">
-        <v>52.95106449634186</v>
+        <v>8.604547980655553</v>
       </c>
       <c r="E4" t="n">
-        <v>12.39015753321636</v>
+        <v>2.013400599147659</v>
       </c>
       <c r="F4" t="n">
-        <v>11.95764903136709</v>
+        <v>1.943117967597153</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>67.64638433093</v>
+        <v>10.99253745377613</v>
       </c>
       <c r="D5" t="n">
-        <v>68.01110459998382</v>
+        <v>11.05180449749737</v>
       </c>
       <c r="E5" t="n">
-        <v>12.39015753321636</v>
+        <v>2.013400599147659</v>
       </c>
       <c r="F5" t="n">
-        <v>11.95764903136709</v>
+        <v>1.943117967597153</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>64.19496365918401</v>
+        <v>10.4316815946174</v>
       </c>
       <c r="D6" t="n">
-        <v>63.99966984336453</v>
+        <v>10.39994634954674</v>
       </c>
       <c r="E6" t="n">
-        <v>12.39015753321636</v>
+        <v>2.013400599147659</v>
       </c>
       <c r="F6" t="n">
-        <v>11.95764903136709</v>
+        <v>1.943117967597153</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>88.43424715250539</v>
+        <v>14.37056516228213</v>
       </c>
       <c r="D7" t="n">
-        <v>87.51130669142903</v>
+        <v>14.22058733735722</v>
       </c>
       <c r="E7" t="n">
-        <v>12.39015753321636</v>
+        <v>2.013400599147659</v>
       </c>
       <c r="F7" t="n">
-        <v>11.95764903136709</v>
+        <v>1.943117967597153</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>74.6694148121769</v>
+        <v>12.13377990697875</v>
       </c>
       <c r="D8" t="n">
-        <v>74.20076008190811</v>
+        <v>12.05762351331007</v>
       </c>
       <c r="E8" t="n">
-        <v>12.39015753321636</v>
+        <v>2.013400599147659</v>
       </c>
       <c r="F8" t="n">
-        <v>11.95764903136709</v>
+        <v>1.943117967597153</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
